--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7170" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1F467A6-CB03-4820-8AE3-86F8ED682B53}"/>
+  <xr:revisionPtr revIDLastSave="7329" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E5274F0-7EB5-402E-8038-9B12CF1133A5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1476" windowWidth="11784" windowHeight="10764" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="0" windowWidth="20124" windowHeight="12336" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AUG26" sheetId="100" r:id="rId1"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId2"/>
+    <sheet name="SEP26" sheetId="101" r:id="rId1"/>
+    <sheet name="AUG26" sheetId="100" r:id="rId2"/>
     <sheet name="JUL26" sheetId="99" r:id="rId3"/>
     <sheet name="JUN26" sheetId="98" r:id="rId4"/>
     <sheet name="MAY26" sheetId="97" r:id="rId5"/>
@@ -25,7 +25,6 @@
     <sheet name="DEC25" sheetId="92" r:id="rId10"/>
     <sheet name="NOV25" sheetId="91" r:id="rId11"/>
     <sheet name="OCT25" sheetId="90" r:id="rId12"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="70">
   <si>
     <t>Name</t>
   </si>
@@ -256,6 +255,9 @@
   <si>
     <t>PROSPECT</t>
   </si>
+  <si>
+    <t>ADVANC</t>
+  </si>
 </sst>
 </file>
 
@@ -453,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -552,7 +554,6 @@
     <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -566,7 +567,6 @@
     <xf numFmtId="170" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -613,10 +613,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -966,20 +962,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE960E6-C7E8-4477-A0CF-2D011FBFDCB7}">
-  <dimension ref="A1:N29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CABE80-A462-4F14-943A-7BDD311B776B}">
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
     <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
     <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
@@ -1012,7 +1008,7 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
+      <c r="I1" s="55"/>
       <c r="J1" s="5"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
@@ -1020,698 +1016,1054 @@
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="28">
-        <v>46254</v>
-      </c>
-      <c r="C2" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>7.0499999999999993E-2</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2*0.9</f>
-        <v>1268.9999999999998</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2</f>
-        <v>1268.9999999999998</v>
-      </c>
-      <c r="I2" s="11"/>
+      <c r="A2" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="74">
+        <v>46267</v>
+      </c>
+      <c r="C2" s="75">
+        <v>120000</v>
+      </c>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="81">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G2" s="77">
+        <f>C2*F2</f>
+        <v>16800</v>
+      </c>
+      <c r="H2" s="77">
+        <f>G2*0.9</f>
+        <v>15120</v>
+      </c>
+      <c r="I2" s="10"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="15"/>
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="41">
-        <f>SUM(H2:H2)</f>
-        <v>1268.9999999999998</v>
-      </c>
-      <c r="I3" s="11"/>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="74">
+        <v>46267</v>
+      </c>
+      <c r="C3" s="75">
+        <v>17500</v>
+      </c>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="77">
+        <f>C3*F3</f>
+        <v>1750</v>
+      </c>
+      <c r="H3" s="77">
+        <f>G3*0.9</f>
+        <v>1575</v>
+      </c>
+      <c r="I3" s="10"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="15"/>
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="77">
-        <v>1.88</v>
-      </c>
-      <c r="E4" s="77">
-        <v>18841.64</v>
-      </c>
-      <c r="F4" s="77">
-        <v>1.9</v>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="74">
+        <v>46268</v>
+      </c>
+      <c r="C4" s="75">
+        <v>400</v>
+      </c>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73">
+        <v>8.69</v>
       </c>
       <c r="G4" s="77">
-        <v>18957.919999999998</v>
+        <f>C4*F4</f>
+        <v>3476</v>
       </c>
       <c r="H4" s="77">
-        <v>116.28</v>
-      </c>
-      <c r="I4" s="11"/>
+        <f>G4*0.9</f>
+        <v>3128.4</v>
+      </c>
+      <c r="I4" s="10"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C5" s="76">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="77">
-        <v>10.5</v>
-      </c>
-      <c r="E5" s="77">
-        <v>29465.119999999999</v>
-      </c>
-      <c r="F5" s="77">
-        <v>11.6</v>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="74">
+        <v>46269</v>
+      </c>
+      <c r="C5" s="75">
+        <v>27000</v>
+      </c>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73">
+        <v>0.05</v>
       </c>
       <c r="G5" s="77">
-        <v>32408.06</v>
+        <f>C5*F5</f>
+        <v>1350</v>
       </c>
       <c r="H5" s="77">
-        <v>2942.94</v>
-      </c>
-      <c r="I5" s="11"/>
+        <f>G5</f>
+        <v>1350</v>
+      </c>
+      <c r="I5" s="10"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="77">
-        <v>3.9</v>
-      </c>
-      <c r="E6" s="77">
-        <v>19543.2</v>
-      </c>
-      <c r="F6" s="77">
-        <v>4.5199999999999996</v>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="74">
+        <v>46269</v>
+      </c>
+      <c r="C6" s="80">
+        <v>24000</v>
+      </c>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73">
+        <v>0.5</v>
       </c>
       <c r="G6" s="77">
-        <v>22549.95</v>
+        <f>C6*F6</f>
+        <v>12000</v>
       </c>
       <c r="H6" s="77">
-        <v>3006.75</v>
-      </c>
-      <c r="I6" s="11"/>
+        <f>G6</f>
+        <v>12000</v>
+      </c>
+      <c r="I6" s="10"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C7" s="76">
-        <v>3200</v>
-      </c>
-      <c r="D7" s="77">
-        <v>9.25</v>
-      </c>
-      <c r="E7" s="77">
-        <v>29665.56</v>
-      </c>
-      <c r="F7" s="77">
-        <v>9.4</v>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="74">
+        <v>46269</v>
+      </c>
+      <c r="C7" s="80">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="78">
+        <v>0.193</v>
       </c>
       <c r="G7" s="77">
-        <v>30013.37</v>
+        <f>C7*F7</f>
+        <v>3860</v>
       </c>
       <c r="H7" s="77">
-        <v>347.81</v>
-      </c>
-      <c r="I7" s="11"/>
+        <f>G7*0.9</f>
+        <v>3474</v>
+      </c>
+      <c r="I7" s="10"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C8" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D8" s="77">
-        <v>1.85</v>
-      </c>
-      <c r="E8" s="77">
-        <v>18540.98</v>
-      </c>
-      <c r="F8" s="77">
-        <v>2.06</v>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="74">
+        <v>46273</v>
+      </c>
+      <c r="C8" s="75">
+        <v>55000</v>
+      </c>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="78">
+        <v>0.28000000000000003</v>
       </c>
       <c r="G8" s="77">
-        <v>20554.38</v>
+        <f>C8*F8</f>
+        <v>15400.000000000002</v>
       </c>
       <c r="H8" s="77">
-        <v>2013.4</v>
-      </c>
-      <c r="I8" s="11"/>
+        <f>G8*0.9</f>
+        <v>13860.000000000002</v>
+      </c>
+      <c r="I8" s="10"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C9" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="77">
-        <v>6.1</v>
-      </c>
-      <c r="E9" s="77">
-        <v>36681.06</v>
-      </c>
-      <c r="F9" s="77">
-        <v>6.7</v>
+      <c r="B9" s="74">
+        <v>46273</v>
+      </c>
+      <c r="C9" s="75">
+        <v>69000</v>
+      </c>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="81">
+        <v>0.1875</v>
       </c>
       <c r="G9" s="77">
-        <v>40110.97</v>
+        <f>C9*F9</f>
+        <v>12937.5</v>
       </c>
       <c r="H9" s="77">
-        <v>3429.91</v>
-      </c>
-      <c r="I9" s="11"/>
+        <f>G9*0.9</f>
+        <v>11643.75</v>
+      </c>
+      <c r="I9" s="10"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C10" s="76">
-        <v>3000</v>
-      </c>
-      <c r="D10" s="77">
-        <v>27.75</v>
-      </c>
-      <c r="E10" s="77">
-        <v>83434.39</v>
-      </c>
-      <c r="F10" s="77">
-        <v>31</v>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="74">
+        <v>46273</v>
+      </c>
+      <c r="C10" s="75">
+        <v>30000</v>
+      </c>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73">
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="G10" s="77">
-        <v>92794.01</v>
+        <f>C10*F10</f>
+        <v>2115</v>
       </c>
       <c r="H10" s="77">
-        <v>9359.6200000000008</v>
-      </c>
-      <c r="I10" s="73"/>
+        <f>G10*0.9</f>
+        <v>1903.5</v>
+      </c>
+      <c r="I10" s="10"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45889</v>
-      </c>
-      <c r="C11" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D11" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E11" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F11" s="77">
-        <v>24.3</v>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="74">
+        <v>46274</v>
+      </c>
+      <c r="C11" s="80">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73">
+        <v>0.20499999999999999</v>
       </c>
       <c r="G11" s="77">
-        <v>96984.72</v>
+        <f>C11*F11</f>
+        <v>2050</v>
       </c>
       <c r="H11" s="77">
-        <v>371.2</v>
-      </c>
+        <f>G11*0.9</f>
+        <v>1845</v>
+      </c>
+      <c r="I11" s="10"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45890</v>
-      </c>
-      <c r="C12" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E12" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F12" s="77">
-        <v>24.3</v>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="74">
+        <v>46274</v>
+      </c>
+      <c r="C12" s="80">
+        <v>45000</v>
+      </c>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73">
+        <v>0.22220000000000001</v>
       </c>
       <c r="G12" s="77">
-        <v>96984.72</v>
+        <f>C12*F12</f>
+        <v>9999</v>
       </c>
       <c r="H12" s="77">
-        <v>371.2</v>
-      </c>
+        <f>G12*0.9</f>
+        <v>8999.1</v>
+      </c>
+      <c r="I12" s="10"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45891</v>
-      </c>
-      <c r="C13" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E13" s="77">
-        <v>120766.9</v>
-      </c>
-      <c r="F13" s="77">
-        <v>24.3</v>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="74">
+        <v>46275</v>
+      </c>
+      <c r="C13" s="75">
+        <v>1200</v>
+      </c>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="78">
+        <v>0.38</v>
       </c>
       <c r="G13" s="77">
-        <v>121230.88</v>
+        <f>C13*F13</f>
+        <v>456</v>
       </c>
       <c r="H13" s="77">
-        <v>463.98</v>
-      </c>
+        <f>G13*0.9</f>
+        <v>410.40000000000003</v>
+      </c>
+      <c r="I13" s="10"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45896</v>
-      </c>
-      <c r="C14" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D14" s="77">
-        <v>7.3</v>
-      </c>
-      <c r="E14" s="77">
-        <v>43897.02</v>
-      </c>
-      <c r="F14" s="77">
-        <v>8.4</v>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="74">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="75">
+        <v>7200</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="78">
+        <v>0.2</v>
       </c>
       <c r="G14" s="77">
-        <v>50288.37</v>
+        <f>C14*F14</f>
+        <v>1440</v>
       </c>
       <c r="H14" s="77">
-        <v>6391.35</v>
-      </c>
+        <f>G14*0.9</f>
+        <v>1296</v>
+      </c>
+      <c r="I14" s="10"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45897</v>
-      </c>
-      <c r="C15" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="77">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E15" s="77">
-        <v>11024.36</v>
-      </c>
-      <c r="F15" s="77">
-        <v>2.2999999999999998</v>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C15" s="75">
+        <v>4000</v>
+      </c>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="78">
+        <v>0.35</v>
       </c>
       <c r="G15" s="77">
-        <v>11474.52</v>
+        <f>C15*F15</f>
+        <v>1400</v>
       </c>
       <c r="H15" s="77">
-        <v>450.16</v>
-      </c>
-      <c r="I15" s="78"/>
+        <f>G15*0.9</f>
+        <v>1260</v>
+      </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E4:E15)</f>
-        <v>605087.27</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G4:G15)</f>
-        <v>634351.87</v>
-      </c>
-      <c r="H16" s="32">
-        <f>SUM(H4:H15)</f>
-        <v>29264.600000000002</v>
-      </c>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C16" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="81">
+        <v>0.45</v>
+      </c>
+      <c r="G16" s="77">
+        <f>C16*F16</f>
+        <v>4500</v>
+      </c>
+      <c r="H16" s="77">
+        <f>G16*0.9</f>
+        <v>4050</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="41">
-        <f>H3+H16</f>
-        <v>30533.600000000002</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-365900.39999999997</v>
-      </c>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C17" s="79">
+        <v>7000</v>
+      </c>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="78">
+        <v>0.27</v>
+      </c>
+      <c r="G17" s="77">
+        <f>C17*F17</f>
+        <v>1890.0000000000002</v>
+      </c>
+      <c r="H17" s="77">
+        <f>G17*0.9</f>
+        <v>1701.0000000000002</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-187350.93</v>
-      </c>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C18" s="80">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="77">
+        <f>C18*F18</f>
+        <v>5000</v>
+      </c>
+      <c r="H18" s="77">
+        <f>G18*0.9</f>
+        <v>4500</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-522717.73</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-553251.32999999996</v>
-      </c>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C19" s="79">
+        <v>25000</v>
+      </c>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="78">
+        <v>0.1133</v>
+      </c>
+      <c r="G19" s="77">
+        <f>C19*F19</f>
+        <v>2832.5</v>
+      </c>
+      <c r="H19" s="77">
+        <f>G19*0.9</f>
+        <v>2549.25</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>377810</v>
-      </c>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C20" s="75">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="78">
+        <v>0.38</v>
+      </c>
+      <c r="G20" s="77">
+        <f>C20*F20</f>
+        <v>380</v>
+      </c>
+      <c r="H20" s="77">
+        <f>G20*0.9</f>
+        <v>342</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="35">
-        <v>10130</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J21" s="7">
-        <v>8610</v>
-      </c>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="74">
+        <v>46276</v>
+      </c>
+      <c r="C21" s="80">
+        <v>4000</v>
+      </c>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="78">
+        <v>0.9</v>
+      </c>
+      <c r="G21" s="77">
+        <f>C21*F21</f>
+        <v>3600</v>
+      </c>
+      <c r="H21" s="77">
+        <v>3472</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>396550</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>386420</v>
-      </c>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="74">
+        <v>46287</v>
+      </c>
+      <c r="C22" s="75">
+        <v>6000</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="78">
+        <v>0.6</v>
+      </c>
+      <c r="G22" s="77">
+        <f>C22*F22</f>
+        <v>3600</v>
+      </c>
+      <c r="H22" s="77">
+        <f>G22*0.9</f>
+        <v>3240</v>
+      </c>
+      <c r="I22" s="10"/>
+      <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="47">
-        <f>H19-H22</f>
-        <v>-919267.73</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-939671.33</v>
-      </c>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A23" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="74">
+        <v>46288</v>
+      </c>
+      <c r="C23" s="75">
+        <v>50000</v>
+      </c>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="78">
+        <v>0.1434</v>
+      </c>
+      <c r="G23" s="77">
+        <f>C23*F23</f>
+        <v>7170</v>
+      </c>
+      <c r="H23" s="77">
+        <f>G23*0.9</f>
+        <v>6453</v>
+      </c>
+      <c r="I23" s="10"/>
+      <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
+      <c r="A24" s="27"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="34">
+        <f>SUM(H2:H23)</f>
+        <v>104172.4</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="6"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-862267.73</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-882671.33</v>
-      </c>
+      <c r="A25" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="74">
+        <v>46286</v>
+      </c>
+      <c r="C25" s="73">
+        <v>3000</v>
+      </c>
+      <c r="D25" s="73">
+        <v>30.25</v>
+      </c>
+      <c r="E25" s="77">
+        <v>90951</v>
+      </c>
+      <c r="F25" s="73">
+        <v>49.25</v>
+      </c>
+      <c r="G25" s="77">
+        <v>147422.75</v>
+      </c>
+      <c r="H25" s="77">
+        <f>G25-E25</f>
+        <v>56471.75</v>
+      </c>
+      <c r="I25" s="56"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="26"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="32">
+        <f>SUM(E25:E25)</f>
+        <v>90951</v>
+      </c>
+      <c r="F26" s="30"/>
+      <c r="G26" s="32">
+        <f>SUM(G25:G25)</f>
+        <v>147422.75</v>
+      </c>
+      <c r="H26" s="32">
+        <f>SUM(H25:H25)</f>
+        <v>56471.75</v>
+      </c>
+      <c r="I26" s="32"/>
       <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D29" s="8"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="11"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="26"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="34">
+        <f>H24+H26</f>
+        <v>160644.15</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="7">
+        <v>50514.94</v>
+      </c>
+      <c r="K27" s="7"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="26"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="7">
+        <f>J29</f>
+        <v>-5690.7140000000072</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="7">
+        <v>-56205.65400000001</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="26"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="41">
+        <f>H27+H28</f>
+        <v>154953.43599999999</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="7">
+        <v>-5690.7140000000072</v>
+      </c>
       <c r="K29" s="7"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="26"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="35">
+        <f>J32</f>
+        <v>237390</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="7">
+        <v>218540</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="26"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="35">
+        <v>30000</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="7">
+        <v>18850</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="26"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="41">
+        <f>H30+H31</f>
+        <v>267390</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="7">
+        <v>237390</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="5"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="45">
+        <f>H29-H32</f>
+        <v>-112436.56400000001</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="7">
+        <v>-243080.71400000001</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="5"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J34" s="7">
+        <v>60000</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="6"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="42">
+        <f>H33+H34</f>
+        <v>-55436.564000000013</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="7">
+        <v>-183080.71400000001</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G36" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H36" s="7">
+        <f>J37</f>
+        <v>271378.40599999996</v>
+      </c>
+      <c r="I36" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="J36" s="32">
+        <v>271378.40599999996</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="M36" s="7"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G37" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="32">
+        <f>H36+H24</f>
+        <v>375550.80599999998</v>
+      </c>
+      <c r="I37" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="J37" s="32">
+        <f>J36+J24</f>
+        <v>271378.40599999996</v>
+      </c>
+      <c r="K37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G38" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" s="32">
+        <f>H37-H32</f>
+        <v>108160.80599999998</v>
+      </c>
+      <c r="I38" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" s="32">
+        <f>J37-J32</f>
+        <v>33988.405999999959</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="54"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="53"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="54"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="32"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C41" s="12"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="10"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N23">
+    <sortCondition ref="B2:B23"/>
+    <sortCondition ref="A2:A23"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
@@ -1900,7 +2252,7 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="83" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="28">
@@ -1938,7 +2290,7 @@
       <c r="B7" s="28">
         <v>45995</v>
       </c>
-      <c r="C7" s="84">
+      <c r="C7" s="82">
         <v>17500</v>
       </c>
       <c r="D7" s="30" t="s">
@@ -2066,7 +2418,7 @@
       <c r="B11" s="28">
         <v>46015</v>
       </c>
-      <c r="C11" s="84">
+      <c r="C11" s="82">
         <v>69000</v>
       </c>
       <c r="D11" s="30" t="s">
@@ -2124,7 +2476,7 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="83" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="28">
@@ -3289,21 +3641,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
-  <dimension ref="A1:N40"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE960E6-C7E8-4477-A0CF-2D011FBFDCB7}">
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
     <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
     <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
@@ -3336,1095 +3688,6 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="75">
-        <v>45903</v>
-      </c>
-      <c r="C2" s="76">
-        <v>120000</v>
-      </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74">
-        <v>0.15454999999999999</v>
-      </c>
-      <c r="G2" s="79">
-        <v>18546</v>
-      </c>
-      <c r="H2" s="79">
-        <v>16691.400000000001</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C3" s="76">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="80">
-        <v>0.31</v>
-      </c>
-      <c r="G3" s="79">
-        <v>372</v>
-      </c>
-      <c r="H3" s="79">
-        <v>339.6</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C4" s="81">
-        <v>17500</v>
-      </c>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="80">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G4" s="79">
-        <v>3587.5</v>
-      </c>
-      <c r="H4" s="79">
-        <v>3228.75</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C5" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="80">
-        <v>0.15</v>
-      </c>
-      <c r="G5" s="79">
-        <v>600</v>
-      </c>
-      <c r="H5" s="79">
-        <v>540</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74">
-        <v>1</v>
-      </c>
-      <c r="G6" s="79">
-        <v>5000</v>
-      </c>
-      <c r="H6" s="79">
-        <v>4500</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C7" s="82">
-        <v>55000</v>
-      </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="80">
-        <v>0.2261</v>
-      </c>
-      <c r="G7" s="79">
-        <v>12435.5</v>
-      </c>
-      <c r="H7" s="79">
-        <v>11191.95</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45909</v>
-      </c>
-      <c r="C8" s="81">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G8" s="79">
-        <v>11110</v>
-      </c>
-      <c r="H8" s="79">
-        <v>9999</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C9" s="81">
-        <v>69000</v>
-      </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="80">
-        <v>0.19650000000000001</v>
-      </c>
-      <c r="G9" s="79">
-        <v>13558.5</v>
-      </c>
-      <c r="H9" s="79">
-        <v>12202.65</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C10" s="82">
-        <v>7200</v>
-      </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G10" s="79">
-        <v>1260</v>
-      </c>
-      <c r="H10" s="79">
-        <v>1134</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C11" s="82">
-        <v>4200</v>
-      </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="83">
-        <v>0.24</v>
-      </c>
-      <c r="G11" s="79">
-        <v>1008</v>
-      </c>
-      <c r="H11" s="79">
-        <v>907.2</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C12" s="81">
-        <v>81000</v>
-      </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="80">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="79">
-        <v>20250</v>
-      </c>
-      <c r="H12" s="79">
-        <v>19926</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C13" s="76">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="79">
-        <v>1350</v>
-      </c>
-      <c r="H13" s="79">
-        <v>1350</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C14" s="76">
-        <v>27000</v>
-      </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="79">
-        <v>13500</v>
-      </c>
-      <c r="H14" s="79">
-        <v>12825</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C15" s="81">
-        <v>17500</v>
-      </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="79">
-        <v>1750</v>
-      </c>
-      <c r="H15" s="79">
-        <v>1575</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C16" s="76">
-        <v>20000</v>
-      </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="80">
-        <v>0.1128</v>
-      </c>
-      <c r="G16" s="79">
-        <v>2256</v>
-      </c>
-      <c r="H16" s="79">
-        <v>2256</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C17" s="76">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="80">
-        <v>0.36</v>
-      </c>
-      <c r="G17" s="79">
-        <v>360</v>
-      </c>
-      <c r="H17" s="79">
-        <v>324</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C18" s="76">
-        <v>8000</v>
-      </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74">
-        <v>0.8</v>
-      </c>
-      <c r="G18" s="79">
-        <v>6400</v>
-      </c>
-      <c r="H18" s="79">
-        <v>5760</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C19" s="76">
-        <v>50000</v>
-      </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="83">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G19" s="79">
-        <v>6625</v>
-      </c>
-      <c r="H19" s="79">
-        <v>5962.5</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C20" s="82">
-        <v>25000</v>
-      </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="83">
-        <v>0.17169999999999999</v>
-      </c>
-      <c r="G20" s="79">
-        <v>4292.5</v>
-      </c>
-      <c r="H20" s="79">
-        <v>3863.25</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34">
-        <f>SUM(H2:H20)</f>
-        <v>114576.29999999999</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="75">
-        <v>45903</v>
-      </c>
-      <c r="C22" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D22" s="74">
-        <v>7.5</v>
-      </c>
-      <c r="E22" s="79">
-        <v>37583.06</v>
-      </c>
-      <c r="F22" s="74">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="G22" s="79">
-        <v>41408.080000000002</v>
-      </c>
-      <c r="H22" s="79">
-        <v>3825.02</v>
-      </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="75">
-        <v>45908</v>
-      </c>
-      <c r="C23" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D23" s="74">
-        <v>24.1</v>
-      </c>
-      <c r="E23" s="79">
-        <v>120766.9</v>
-      </c>
-      <c r="F23" s="74">
-        <v>23.4</v>
-      </c>
-      <c r="G23" s="79">
-        <v>116740.86</v>
-      </c>
-      <c r="H23" s="79">
-        <v>-4026.04</v>
-      </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C24" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D24" s="74">
-        <v>23.2</v>
-      </c>
-      <c r="E24" s="79">
-        <v>116256.93</v>
-      </c>
-      <c r="F24" s="74">
-        <v>23.4</v>
-      </c>
-      <c r="G24" s="79">
-        <v>116740.86</v>
-      </c>
-      <c r="H24" s="74">
-        <v>483.93</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C25" s="74">
-        <v>4000</v>
-      </c>
-      <c r="D25" s="74">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="79">
-        <v>92604.66</v>
-      </c>
-      <c r="F25" s="74">
-        <v>25.75</v>
-      </c>
-      <c r="G25" s="79">
-        <v>102771.87</v>
-      </c>
-      <c r="H25" s="79">
-        <v>10167.209999999999</v>
-      </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C26" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D26" s="74">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E26" s="79">
-        <v>44097.46</v>
-      </c>
-      <c r="F26" s="74">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G26" s="79">
-        <v>48392.57</v>
-      </c>
-      <c r="H26" s="79">
-        <v>4295.1099999999997</v>
-      </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32">
-        <f>SUM(E22:E26)</f>
-        <v>411309.01000000007</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32">
-        <f>SUM(G22:G26)</f>
-        <v>426054.24</v>
-      </c>
-      <c r="H27" s="32">
-        <f>SUM(H22:H26)</f>
-        <v>14745.23</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="34">
-        <f>H21+H27</f>
-        <v>129321.52999999998</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="41">
-        <f>H28+H29</f>
-        <v>-393315.2</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="35">
-        <v>62010</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="41">
-        <f>H31+H32</f>
-        <v>458560</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="5"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="45">
-        <f>H30-H33</f>
-        <v>-851875.2</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K34" s="7"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K35" s="7"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="6"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="42">
-        <f>H34+H35</f>
-        <v>-794875.2</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C38" s="29">
-        <v>24000</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="51">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="G38" s="31">
-        <f>C38*F38</f>
-        <v>957.59999999999991</v>
-      </c>
-      <c r="H38" s="53">
-        <f>G38*0.9</f>
-        <v>861.83999999999992</v>
-      </c>
-      <c r="K38" s="7"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="28">
-        <v>45530</v>
-      </c>
-      <c r="C39" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="37">
-        <v>0.19</v>
-      </c>
-      <c r="G39" s="31">
-        <f>C39*F39</f>
-        <v>5700</v>
-      </c>
-      <c r="H39" s="32">
-        <f>G39</f>
-        <v>5700</v>
-      </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C40" s="12"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="10"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
-    <sortCondition ref="A2:A20"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="3"/>
       <c r="J1" s="5"/>
       <c r="K1" s="6"/>
@@ -4434,28 +3697,27 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B2" s="28">
-        <v>45897</v>
+        <v>46254</v>
       </c>
       <c r="C2" s="29">
-        <v>600</v>
+        <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="72">
-        <v>2.5</v>
+      <c r="F2" s="37">
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1500</v>
+        <f>C2*F2*0.9</f>
+        <v>1268.9999999999998</v>
       </c>
       <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7"/>
@@ -4474,7 +3736,7 @@
       <c r="G3" s="31"/>
       <c r="H3" s="41">
         <f>SUM(H2:H2)</f>
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="7"/>
@@ -4484,649 +3746,341 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="77">
-        <v>1.88</v>
-      </c>
-      <c r="E4" s="77">
-        <v>18841.64</v>
-      </c>
-      <c r="F4" s="77">
-        <v>1.9</v>
-      </c>
-      <c r="G4" s="77">
-        <v>18957.919999999998</v>
-      </c>
-      <c r="H4" s="77">
-        <v>116.28</v>
-      </c>
-      <c r="I4" s="11"/>
+      <c r="A4" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="74">
+        <v>46254</v>
+      </c>
+      <c r="C4" s="75">
+        <v>3000</v>
+      </c>
+      <c r="D4" s="76">
+        <v>28</v>
+      </c>
+      <c r="E4" s="76">
+        <v>84186.05</v>
+      </c>
+      <c r="F4" s="76">
+        <v>45</v>
+      </c>
+      <c r="G4" s="76">
+        <v>134700.99</v>
+      </c>
+      <c r="H4" s="76">
+        <v>50514.94</v>
+      </c>
+      <c r="I4" s="72"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C5" s="76">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="77">
-        <v>10.5</v>
-      </c>
-      <c r="E5" s="77">
-        <v>29465.119999999999</v>
-      </c>
-      <c r="F5" s="77">
-        <v>11.6</v>
-      </c>
-      <c r="G5" s="77">
-        <v>32408.06</v>
-      </c>
-      <c r="H5" s="77">
-        <v>2942.94</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>84186.05</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>134700.99</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>50514.94</v>
+      </c>
       <c r="K5" s="7"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="77">
-        <v>3.9</v>
-      </c>
-      <c r="E6" s="77">
-        <v>19543.2</v>
-      </c>
-      <c r="F6" s="77">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="G6" s="77">
-        <v>22549.95</v>
-      </c>
-      <c r="H6" s="77">
-        <v>3006.75</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="41">
+        <f>H3+H5</f>
+        <v>50514.94</v>
+      </c>
+      <c r="I6" s="91" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="32">
+        <v>1277.9999999999998</v>
+      </c>
       <c r="K6" s="7"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C7" s="76">
-        <v>3200</v>
-      </c>
-      <c r="D7" s="77">
-        <v>9.25</v>
-      </c>
-      <c r="E7" s="77">
-        <v>29665.56</v>
-      </c>
-      <c r="F7" s="77">
-        <v>9.4</v>
-      </c>
-      <c r="G7" s="77">
-        <v>30013.37</v>
-      </c>
-      <c r="H7" s="77">
-        <v>347.81</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <f>J8</f>
+        <v>-56205.65400000001</v>
+      </c>
+      <c r="I7" s="91" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="32">
+        <v>-57483.65400000001</v>
+      </c>
       <c r="K7" s="7"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C8" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D8" s="77">
-        <v>1.85</v>
-      </c>
-      <c r="E8" s="77">
-        <v>18540.98</v>
-      </c>
-      <c r="F8" s="77">
-        <v>2.06</v>
-      </c>
-      <c r="G8" s="77">
-        <v>20554.38</v>
-      </c>
-      <c r="H8" s="77">
-        <v>2013.4</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="41">
+        <f>H6+H7</f>
+        <v>-5690.7140000000072</v>
+      </c>
+      <c r="I8" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="32">
+        <v>-56205.65400000001</v>
+      </c>
       <c r="K8" s="7"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C9" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="77">
-        <v>6.1</v>
-      </c>
-      <c r="E9" s="77">
-        <v>36681.06</v>
-      </c>
-      <c r="F9" s="77">
-        <v>6.7</v>
-      </c>
-      <c r="G9" s="77">
-        <v>40110.97</v>
-      </c>
-      <c r="H9" s="77">
-        <v>3429.91</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="32">
+        <f>J11</f>
+        <v>218540</v>
+      </c>
+      <c r="I9" s="91" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="32">
+        <v>184230</v>
+      </c>
       <c r="K9" s="7"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C10" s="76">
-        <v>3000</v>
-      </c>
-      <c r="D10" s="77">
-        <v>27.75</v>
-      </c>
-      <c r="E10" s="77">
-        <v>83434.39</v>
-      </c>
-      <c r="F10" s="77">
-        <v>31</v>
-      </c>
-      <c r="G10" s="77">
-        <v>92794.01</v>
-      </c>
-      <c r="H10" s="77">
-        <v>9359.6200000000008</v>
-      </c>
-      <c r="I10" s="73"/>
-      <c r="J10" s="7"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="35">
+        <v>18850</v>
+      </c>
+      <c r="I10" s="91" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="32">
+        <v>34310</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45889</v>
-      </c>
-      <c r="C11" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D11" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E11" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F11" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G11" s="77">
-        <v>96984.72</v>
-      </c>
-      <c r="H11" s="77">
-        <v>371.2</v>
-      </c>
-      <c r="J11" s="7"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>237390</v>
+      </c>
+      <c r="I11" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="32">
+        <v>218540</v>
+      </c>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45890</v>
-      </c>
-      <c r="C12" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E12" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F12" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G12" s="77">
-        <v>96984.72</v>
-      </c>
-      <c r="H12" s="77">
-        <v>371.2</v>
-      </c>
-      <c r="J12" s="7"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="47">
+        <f>H8-H11</f>
+        <v>-243080.71400000001</v>
+      </c>
+      <c r="I12" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="32">
+        <v>-274745.65399999998</v>
+      </c>
       <c r="K12" s="7"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45891</v>
-      </c>
-      <c r="C13" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E13" s="77">
-        <v>120766.9</v>
-      </c>
-      <c r="F13" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G13" s="77">
-        <v>121230.88</v>
-      </c>
-      <c r="H13" s="77">
-        <v>463.98</v>
-      </c>
-      <c r="J13" s="7"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="32">
+        <v>60000</v>
+      </c>
+      <c r="I13" s="91" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="32">
+        <v>60000</v>
+      </c>
       <c r="K13" s="7"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45896</v>
-      </c>
-      <c r="C14" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D14" s="77">
-        <v>7.3</v>
-      </c>
-      <c r="E14" s="77">
-        <v>43897.02</v>
-      </c>
-      <c r="F14" s="77">
-        <v>8.4</v>
-      </c>
-      <c r="G14" s="77">
-        <v>50288.37</v>
-      </c>
-      <c r="H14" s="77">
-        <v>6391.35</v>
-      </c>
-      <c r="J14" s="7"/>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="42">
+        <f>H12+H13</f>
+        <v>-183080.71400000001</v>
+      </c>
+      <c r="I14" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="32">
+        <v>-214745.65399999998</v>
+      </c>
       <c r="K14" s="7"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45897</v>
-      </c>
-      <c r="C15" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="77">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E15" s="77">
-        <v>11024.36</v>
-      </c>
-      <c r="F15" s="77">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G15" s="77">
-        <v>11474.52</v>
-      </c>
-      <c r="H15" s="77">
-        <v>450.16</v>
-      </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="7"/>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G15" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="32">
+        <v>271378.40599999996</v>
+      </c>
+      <c r="I15" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="32">
+        <v>270100.40599999996</v>
+      </c>
       <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E4:E15)</f>
-        <v>605087.27</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G4:G15)</f>
-        <v>634351.87</v>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G16" s="91" t="s">
+        <v>64</v>
       </c>
       <c r="H16" s="32">
-        <f>SUM(H4:H15)</f>
-        <v>29264.600000000002</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="41">
-        <f>H3+H16</f>
-        <v>30614.600000000002</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-187350.93</v>
-      </c>
+        <f>H15+H3</f>
+        <v>271378.40599999996</v>
+      </c>
+      <c r="I16" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="32">
+        <v>271378.40599999996</v>
+      </c>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G17" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="32">
+        <f>H16-H11</f>
+        <v>33988.405999999959</v>
+      </c>
+      <c r="I17" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="32">
+        <v>52838.405999999959</v>
+      </c>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="11"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-522636.73</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>377810</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="35">
-        <v>10130</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J21" s="7">
-        <v>8610</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>396550</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="47">
-        <f>H19-H22</f>
-        <v>-919186.73</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-939671.33</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="6"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-862186.73</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-882671.33</v>
-      </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D29" s="8"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -5513,7 +4467,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="7">
-        <v>270100.40599999996</v>
+        <v>270100.40600000002</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>63</v>
@@ -5530,7 +4484,7 @@
       </c>
       <c r="H16" s="32">
         <f>H15+H3</f>
-        <v>271378.40599999996</v>
+        <v>271378.40600000002</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>64</v>
@@ -5546,7 +4500,7 @@
       </c>
       <c r="H17" s="32">
         <f>H16-H11</f>
-        <v>52838.405999999959</v>
+        <v>52838.406000000017</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>65</v>
@@ -5701,7 +4655,7 @@
       <c r="B4" s="28">
         <v>46183</v>
       </c>
-      <c r="C4" s="84">
+      <c r="C4" s="82">
         <v>45000</v>
       </c>
       <c r="D4" s="30" t="s">
@@ -5765,7 +4719,7 @@
       <c r="B6" s="28">
         <v>46184</v>
       </c>
-      <c r="C6" s="97">
+      <c r="C6" s="95">
         <v>69000</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -5829,7 +4783,7 @@
       <c r="B8" s="28">
         <v>46189</v>
       </c>
-      <c r="C8" s="84">
+      <c r="C8" s="82">
         <v>25000</v>
       </c>
       <c r="D8" s="30" t="s">
@@ -5861,7 +4815,7 @@
       <c r="B9" s="28">
         <v>46191</v>
       </c>
-      <c r="C9" s="97">
+      <c r="C9" s="95">
         <v>50000</v>
       </c>
       <c r="D9" s="30" t="s">
@@ -6263,7 +5217,7 @@
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
     <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="90" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="88" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.125" style="13" bestFit="1" customWidth="1"/>
@@ -6291,7 +5245,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="84" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -6323,7 +5277,7 @@
       <c r="E2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="87">
+      <c r="F2" s="85">
         <v>0.43</v>
       </c>
       <c r="G2" s="31">
@@ -6348,7 +5302,7 @@
       <c r="B3" s="69">
         <v>46149</v>
       </c>
-      <c r="C3" s="97">
+      <c r="C3" s="95">
         <v>75000</v>
       </c>
       <c r="D3" s="30" t="s">
@@ -6357,7 +5311,7 @@
       <c r="E3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="89">
+      <c r="F3" s="87">
         <v>0.7</v>
       </c>
       <c r="G3" s="31">
@@ -6390,7 +5344,7 @@
       <c r="E4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="86">
         <v>0.26</v>
       </c>
       <c r="G4" s="31">
@@ -6424,7 +5378,7 @@
       <c r="E5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="87">
         <v>0.5</v>
       </c>
       <c r="G5" s="31">
@@ -6449,7 +5403,7 @@
       <c r="B6" s="69">
         <v>46154</v>
       </c>
-      <c r="C6" s="84">
+      <c r="C6" s="82">
         <v>17500</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -6458,7 +5412,7 @@
       <c r="E6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="87">
         <v>0.38</v>
       </c>
       <c r="G6" s="31">
@@ -6492,7 +5446,7 @@
       <c r="E7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="93">
         <v>0.35</v>
       </c>
       <c r="G7" s="31">
@@ -6526,7 +5480,7 @@
       <c r="E8" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="96">
+      <c r="F8" s="94">
         <v>1.5</v>
       </c>
       <c r="G8" s="31">
@@ -6559,7 +5513,7 @@
       <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="93">
         <v>1.17</v>
       </c>
       <c r="G9" s="31">
@@ -6592,7 +5546,7 @@
       <c r="E10" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="87">
+      <c r="F10" s="85">
         <v>0.48</v>
       </c>
       <c r="G10" s="31">
@@ -6626,7 +5580,7 @@
       <c r="E11" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="87">
         <v>0.3</v>
       </c>
       <c r="G11" s="31">
@@ -6660,7 +5614,7 @@
       <c r="E12" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="85">
         <v>0.25</v>
       </c>
       <c r="G12" s="31">
@@ -6694,7 +5648,7 @@
       <c r="E13" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="87">
+      <c r="F13" s="85">
         <v>0.17499999999999999</v>
       </c>
       <c r="G13" s="31">
@@ -6728,7 +5682,7 @@
       <c r="E14" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="87">
         <v>0.138295</v>
       </c>
       <c r="G14" s="31">
@@ -6761,7 +5715,7 @@
       <c r="E15" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="87">
         <v>0.39</v>
       </c>
       <c r="G15" s="31">
@@ -6795,7 +5749,7 @@
       <c r="E16" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="87">
         <v>0.08</v>
       </c>
       <c r="G16" s="31">
@@ -6829,7 +5783,7 @@
       <c r="E17" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="87">
+      <c r="F17" s="85">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G17" s="31">
@@ -6853,7 +5807,7 @@
       <c r="C18" s="29"/>
       <c r="D18" s="30"/>
       <c r="E18" s="31"/>
-      <c r="F18" s="87"/>
+      <c r="F18" s="85"/>
       <c r="G18" s="31"/>
       <c r="H18" s="34">
         <f>SUM(H2:H17)</f>
@@ -6882,7 +5836,7 @@
       <c r="E19" s="31">
         <v>40088.6</v>
       </c>
-      <c r="F19" s="87">
+      <c r="F19" s="85">
         <v>7.8</v>
       </c>
       <c r="G19" s="31">
@@ -6908,7 +5862,7 @@
         <f>SUM(E19:E19)</f>
         <v>40088.6</v>
       </c>
-      <c r="F20" s="87"/>
+      <c r="F20" s="85"/>
       <c r="G20" s="32">
         <f>SUM(G19:G19)</f>
         <v>38913.620000000003</v>
@@ -6930,7 +5884,7 @@
       <c r="C21" s="29"/>
       <c r="D21" s="33"/>
       <c r="E21" s="32"/>
-      <c r="F21" s="87"/>
+      <c r="F21" s="85"/>
       <c r="G21" s="32" t="s">
         <v>12</v>
       </c>
@@ -6955,7 +5909,7 @@
       <c r="C22" s="29"/>
       <c r="D22" s="33"/>
       <c r="E22" s="32"/>
-      <c r="F22" s="87"/>
+      <c r="F22" s="85"/>
       <c r="G22" s="32" t="s">
         <v>16</v>
       </c>
@@ -6979,7 +5933,7 @@
       <c r="C23" s="29"/>
       <c r="D23" s="33"/>
       <c r="E23" s="32"/>
-      <c r="F23" s="87"/>
+      <c r="F23" s="85"/>
       <c r="G23" s="32" t="s">
         <v>28</v>
       </c>
@@ -7004,7 +5958,7 @@
       <c r="C24" s="29"/>
       <c r="D24" s="33"/>
       <c r="E24" s="32"/>
-      <c r="F24" s="87"/>
+      <c r="F24" s="85"/>
       <c r="G24" s="32" t="s">
         <v>13</v>
       </c>
@@ -7028,7 +5982,7 @@
       <c r="C25" s="29"/>
       <c r="D25" s="33"/>
       <c r="E25" s="32"/>
-      <c r="F25" s="87"/>
+      <c r="F25" s="85"/>
       <c r="G25" s="32" t="s">
         <v>46</v>
       </c>
@@ -7052,7 +6006,7 @@
       <c r="C26" s="29"/>
       <c r="D26" s="33"/>
       <c r="E26" s="32"/>
-      <c r="F26" s="87"/>
+      <c r="F26" s="85"/>
       <c r="G26" s="32" t="s">
         <v>14</v>
       </c>
@@ -7077,7 +6031,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="90"/>
+      <c r="F27" s="88"/>
       <c r="G27" s="32" t="s">
         <v>15</v>
       </c>
@@ -7102,7 +6056,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="9"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="90"/>
+      <c r="F28" s="88"/>
       <c r="G28" s="38" t="s">
         <v>30</v>
       </c>
@@ -7126,7 +6080,7 @@
       <c r="C29" s="8"/>
       <c r="D29" s="10"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="90"/>
+      <c r="F29" s="88"/>
       <c r="G29" s="38" t="s">
         <v>31</v>
       </c>
@@ -7572,7 +6526,7 @@
       <c r="I14" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="94">
+      <c r="J14" s="92">
         <v>60000</v>
       </c>
       <c r="K14" s="15"/>
@@ -7674,7 +6628,7 @@
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="90" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="88" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.75" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.75" style="11" bestFit="1" customWidth="1"/>
@@ -7703,7 +6657,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="84" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -7712,8 +6666,8 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
@@ -7732,7 +6686,7 @@
       <c r="E2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="89">
+      <c r="F2" s="87">
         <v>0.22412299999999999</v>
       </c>
       <c r="G2" s="31">
@@ -7763,7 +6717,7 @@
       <c r="E3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="87">
+      <c r="F3" s="85">
         <v>0.22220000000000001</v>
       </c>
       <c r="G3" s="31">
@@ -7794,7 +6748,7 @@
       <c r="E4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="86">
         <v>0.17829999999999999</v>
       </c>
       <c r="G4" s="31">
@@ -7825,7 +6779,7 @@
       <c r="E5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="87">
         <v>0.12189999999999999</v>
       </c>
       <c r="G5" s="31">
@@ -7856,7 +6810,7 @@
       <c r="E6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="87">
+      <c r="F6" s="85">
         <v>0.1212</v>
       </c>
       <c r="G6" s="31">
@@ -7886,7 +6840,7 @@
       <c r="E7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="87">
+      <c r="F7" s="85">
         <v>7.4800000000000005E-2</v>
       </c>
       <c r="G7" s="31">
@@ -7916,7 +6870,7 @@
       <c r="E8" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="86">
         <v>0.17549999999999999</v>
       </c>
       <c r="G8" s="31">
@@ -7947,7 +6901,7 @@
       <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="87">
         <v>0.27939999999999998</v>
       </c>
       <c r="G9" s="31">
@@ -7968,7 +6922,7 @@
       <c r="C10" s="29"/>
       <c r="D10" s="30"/>
       <c r="E10" s="31"/>
-      <c r="F10" s="87"/>
+      <c r="F10" s="85"/>
       <c r="G10" s="31"/>
       <c r="H10" s="32">
         <f>SUM(H2:H9)</f>
@@ -7994,7 +6948,7 @@
       <c r="E11" s="31">
         <v>185910.87</v>
       </c>
-      <c r="F11" s="87">
+      <c r="F11" s="85">
         <v>11.1</v>
       </c>
       <c r="G11" s="31">
@@ -8004,7 +6958,7 @@
         <f>G11-E11</f>
         <v>7908.8800000000047</v>
       </c>
-      <c r="I11" s="93"/>
+      <c r="I11" s="91"/>
       <c r="J11" s="32"/>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
@@ -8027,7 +6981,7 @@
       <c r="E12" s="31">
         <v>224897.03</v>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="85">
         <v>6.25</v>
       </c>
       <c r="G12" s="31">
@@ -8037,7 +6991,7 @@
         <f>G12-E12</f>
         <v>-182491.16999999998</v>
       </c>
-      <c r="I12" s="93"/>
+      <c r="I12" s="91"/>
       <c r="J12" s="32"/>
       <c r="K12" s="7"/>
       <c r="L12" s="15"/>
@@ -8060,7 +7014,7 @@
       <c r="E13" s="31">
         <v>243538.22</v>
       </c>
-      <c r="F13" s="87">
+      <c r="F13" s="85">
         <v>172</v>
       </c>
       <c r="G13" s="31">
@@ -8070,7 +7024,7 @@
         <f>G13-E13</f>
         <v>-140566.79</v>
       </c>
-      <c r="I13" s="93"/>
+      <c r="I13" s="91"/>
       <c r="J13" s="32"/>
       <c r="K13" s="7"/>
       <c r="L13" s="15"/>
@@ -8086,7 +7040,7 @@
         <f>SUM(E11:E13)</f>
         <v>654346.12</v>
       </c>
-      <c r="F14" s="87"/>
+      <c r="F14" s="85"/>
       <c r="G14" s="32">
         <f>SUM(G11:G13)</f>
         <v>339197.04</v>
@@ -8106,7 +7060,7 @@
       <c r="C15" s="29"/>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="87"/>
+      <c r="F15" s="85"/>
       <c r="G15" s="32" t="s">
         <v>12</v>
       </c>
@@ -8114,7 +7068,7 @@
         <f>H10+H14</f>
         <v>-243272.66599999997</v>
       </c>
-      <c r="I15" s="93" t="s">
+      <c r="I15" s="91" t="s">
         <v>12</v>
       </c>
       <c r="J15" s="60">
@@ -8127,7 +7081,7 @@
       <c r="C16" s="29"/>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="87"/>
+      <c r="F16" s="85"/>
       <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
@@ -8148,7 +7102,7 @@
       <c r="C17" s="29"/>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="87"/>
+      <c r="F17" s="85"/>
       <c r="G17" s="60" t="s">
         <v>28</v>
       </c>
@@ -8170,7 +7124,7 @@
       <c r="C18" s="29"/>
       <c r="D18" s="33"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="87"/>
+      <c r="F18" s="85"/>
       <c r="G18" s="32" t="s">
         <v>13</v>
       </c>
@@ -8191,7 +7145,7 @@
       <c r="C19" s="29"/>
       <c r="D19" s="33"/>
       <c r="E19" s="32"/>
-      <c r="F19" s="87"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="32" t="s">
         <v>24</v>
       </c>
@@ -8212,7 +7166,7 @@
       <c r="C20" s="29"/>
       <c r="D20" s="33"/>
       <c r="E20" s="32"/>
-      <c r="F20" s="87"/>
+      <c r="F20" s="85"/>
       <c r="G20" s="32" t="s">
         <v>14</v>
       </c>
@@ -8234,11 +7188,11 @@
       <c r="C21" s="29"/>
       <c r="D21" s="33"/>
       <c r="E21" s="32"/>
-      <c r="F21" s="87"/>
+      <c r="F21" s="85"/>
       <c r="G21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="91">
+      <c r="H21" s="89">
         <f>H17-H20</f>
         <v>-352702.66599999997</v>
       </c>
@@ -8256,11 +7210,11 @@
       <c r="C22" s="29"/>
       <c r="D22" s="33"/>
       <c r="E22" s="32"/>
-      <c r="F22" s="87"/>
+      <c r="F22" s="85"/>
       <c r="G22" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="94">
+      <c r="H22" s="92">
         <v>60000</v>
       </c>
       <c r="I22" s="35" t="s">
@@ -8277,7 +7231,7 @@
       <c r="C23" s="29"/>
       <c r="D23" s="33"/>
       <c r="E23" s="32"/>
-      <c r="F23" s="87"/>
+      <c r="F23" s="85"/>
       <c r="G23" s="60" t="s">
         <v>31</v>
       </c>
@@ -8285,7 +7239,7 @@
         <f>H21+H22</f>
         <v>-292702.66599999997</v>
       </c>
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="91" t="s">
         <v>31</v>
       </c>
       <c r="J23" s="60">
@@ -8298,14 +7252,14 @@
       <c r="C24" s="29"/>
       <c r="D24" s="33"/>
       <c r="E24" s="32"/>
-      <c r="F24" s="87"/>
+      <c r="F24" s="85"/>
       <c r="G24" s="32" t="s">
         <v>63</v>
       </c>
       <c r="H24" s="32">
         <v>0</v>
       </c>
-      <c r="I24" s="93"/>
+      <c r="I24" s="91"/>
       <c r="J24" s="32"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -8314,7 +7268,7 @@
       <c r="C25" s="29"/>
       <c r="D25" s="33"/>
       <c r="E25" s="32"/>
-      <c r="F25" s="87"/>
+      <c r="F25" s="85"/>
       <c r="G25" s="32" t="s">
         <v>64</v>
       </c>
@@ -8322,7 +7276,7 @@
         <f>H24+H10</f>
         <v>71876.41399999999</v>
       </c>
-      <c r="I25" s="93"/>
+      <c r="I25" s="91"/>
       <c r="J25" s="32"/>
     </row>
     <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -8331,7 +7285,7 @@
       <c r="C26" s="29"/>
       <c r="D26" s="33"/>
       <c r="E26" s="32"/>
-      <c r="F26" s="87"/>
+      <c r="F26" s="85"/>
       <c r="G26" s="32" t="s">
         <v>65</v>
       </c>
@@ -8339,7 +7293,7 @@
         <f>H25-H20</f>
         <v>-26293.58600000001</v>
       </c>
-      <c r="I26" s="93"/>
+      <c r="I26" s="91"/>
       <c r="J26" s="32"/>
     </row>
   </sheetData>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7329" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E5274F0-7EB5-402E-8038-9B12CF1133A5}"/>
+  <xr:revisionPtr revIDLastSave="7330" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3298DA1-2A8C-4C33-8A55-27FBF34598A7}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="0" windowWidth="20124" windowHeight="12336" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8976" yWindow="504" windowWidth="12216" windowHeight="9564" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEP26" sheetId="101" r:id="rId1"/>
@@ -615,6 +615,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1031,7 +1035,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G2" s="77">
-        <f>C2*F2</f>
+        <f t="shared" ref="G2:G23" si="0">C2*F2</f>
         <v>16800</v>
       </c>
       <c r="H2" s="77">
@@ -1061,7 +1065,7 @@
         <v>0.1</v>
       </c>
       <c r="G3" s="77">
-        <f>C3*F3</f>
+        <f t="shared" si="0"/>
         <v>1750</v>
       </c>
       <c r="H3" s="77">
@@ -1091,7 +1095,7 @@
         <v>8.69</v>
       </c>
       <c r="G4" s="77">
-        <f>C4*F4</f>
+        <f t="shared" si="0"/>
         <v>3476</v>
       </c>
       <c r="H4" s="77">
@@ -1121,7 +1125,7 @@
         <v>0.05</v>
       </c>
       <c r="G5" s="77">
-        <f>C5*F5</f>
+        <f t="shared" si="0"/>
         <v>1350</v>
       </c>
       <c r="H5" s="77">
@@ -1151,7 +1155,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="77">
-        <f>C6*F6</f>
+        <f t="shared" si="0"/>
         <v>12000</v>
       </c>
       <c r="H6" s="77">
@@ -1181,11 +1185,11 @@
         <v>0.193</v>
       </c>
       <c r="G7" s="77">
-        <f>C7*F7</f>
+        <f t="shared" si="0"/>
         <v>3860</v>
       </c>
       <c r="H7" s="77">
-        <f>G7*0.9</f>
+        <f t="shared" ref="H7:H20" si="1">G7*0.9</f>
         <v>3474</v>
       </c>
       <c r="I7" s="10"/>
@@ -1211,11 +1215,11 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G8" s="77">
-        <f>C8*F8</f>
+        <f t="shared" si="0"/>
         <v>15400.000000000002</v>
       </c>
       <c r="H8" s="77">
-        <f>G8*0.9</f>
+        <f t="shared" si="1"/>
         <v>13860.000000000002</v>
       </c>
       <c r="I8" s="10"/>
@@ -1241,11 +1245,11 @@
         <v>0.1875</v>
       </c>
       <c r="G9" s="77">
-        <f>C9*F9</f>
+        <f t="shared" si="0"/>
         <v>12937.5</v>
       </c>
       <c r="H9" s="77">
-        <f>G9*0.9</f>
+        <f t="shared" si="1"/>
         <v>11643.75</v>
       </c>
       <c r="I9" s="10"/>
@@ -1271,11 +1275,11 @@
         <v>7.0499999999999993E-2</v>
       </c>
       <c r="G10" s="77">
-        <f>C10*F10</f>
+        <f t="shared" si="0"/>
         <v>2115</v>
       </c>
       <c r="H10" s="77">
-        <f>G10*0.9</f>
+        <f t="shared" si="1"/>
         <v>1903.5</v>
       </c>
       <c r="I10" s="10"/>
@@ -1301,11 +1305,11 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="G11" s="77">
-        <f>C11*F11</f>
+        <f t="shared" si="0"/>
         <v>2050</v>
       </c>
       <c r="H11" s="77">
-        <f>G11*0.9</f>
+        <f t="shared" si="1"/>
         <v>1845</v>
       </c>
       <c r="I11" s="10"/>
@@ -1331,11 +1335,11 @@
         <v>0.22220000000000001</v>
       </c>
       <c r="G12" s="77">
-        <f>C12*F12</f>
+        <f t="shared" si="0"/>
         <v>9999</v>
       </c>
       <c r="H12" s="77">
-        <f>G12*0.9</f>
+        <f t="shared" si="1"/>
         <v>8999.1</v>
       </c>
       <c r="I12" s="10"/>
@@ -1361,11 +1365,11 @@
         <v>0.38</v>
       </c>
       <c r="G13" s="77">
-        <f>C13*F13</f>
+        <f t="shared" si="0"/>
         <v>456</v>
       </c>
       <c r="H13" s="77">
-        <f>G13*0.9</f>
+        <f t="shared" si="1"/>
         <v>410.40000000000003</v>
       </c>
       <c r="I13" s="10"/>
@@ -1391,11 +1395,11 @@
         <v>0.2</v>
       </c>
       <c r="G14" s="77">
-        <f>C14*F14</f>
+        <f t="shared" si="0"/>
         <v>1440</v>
       </c>
       <c r="H14" s="77">
-        <f>G14*0.9</f>
+        <f t="shared" si="1"/>
         <v>1296</v>
       </c>
       <c r="I14" s="10"/>
@@ -1421,11 +1425,11 @@
         <v>0.35</v>
       </c>
       <c r="G15" s="77">
-        <f>C15*F15</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="H15" s="77">
-        <f>G15*0.9</f>
+        <f t="shared" si="1"/>
         <v>1260</v>
       </c>
       <c r="I15" s="10"/>
@@ -1451,11 +1455,11 @@
         <v>0.45</v>
       </c>
       <c r="G16" s="77">
-        <f>C16*F16</f>
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="H16" s="77">
-        <f>G16*0.9</f>
+        <f t="shared" si="1"/>
         <v>4050</v>
       </c>
       <c r="I16" s="10"/>
@@ -1481,11 +1485,11 @@
         <v>0.27</v>
       </c>
       <c r="G17" s="77">
-        <f>C17*F17</f>
+        <f t="shared" si="0"/>
         <v>1890.0000000000002</v>
       </c>
       <c r="H17" s="77">
-        <f>G17*0.9</f>
+        <f t="shared" si="1"/>
         <v>1701.0000000000002</v>
       </c>
       <c r="I17" s="10"/>
@@ -1511,11 +1515,11 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="77">
-        <f>C18*F18</f>
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="H18" s="77">
-        <f>G18*0.9</f>
+        <f t="shared" si="1"/>
         <v>4500</v>
       </c>
       <c r="I18" s="10"/>
@@ -1541,11 +1545,11 @@
         <v>0.1133</v>
       </c>
       <c r="G19" s="77">
-        <f>C19*F19</f>
+        <f t="shared" si="0"/>
         <v>2832.5</v>
       </c>
       <c r="H19" s="77">
-        <f>G19*0.9</f>
+        <f t="shared" si="1"/>
         <v>2549.25</v>
       </c>
       <c r="I19" s="10"/>
@@ -1571,11 +1575,11 @@
         <v>0.38</v>
       </c>
       <c r="G20" s="77">
-        <f>C20*F20</f>
+        <f t="shared" si="0"/>
         <v>380</v>
       </c>
       <c r="H20" s="77">
-        <f>G20*0.9</f>
+        <f t="shared" si="1"/>
         <v>342</v>
       </c>
       <c r="I20" s="10"/>
@@ -1601,7 +1605,7 @@
         <v>0.9</v>
       </c>
       <c r="G21" s="77">
-        <f>C21*F21</f>
+        <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="H21" s="77">
@@ -1630,7 +1634,7 @@
         <v>0.6</v>
       </c>
       <c r="G22" s="77">
-        <f>C22*F22</f>
+        <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="H22" s="77">
@@ -1660,7 +1664,7 @@
         <v>0.1434</v>
       </c>
       <c r="G23" s="77">
-        <f>C23*F23</f>
+        <f t="shared" si="0"/>
         <v>7170</v>
       </c>
       <c r="H23" s="77">
@@ -1857,7 +1861,7 @@
         <v>52</v>
       </c>
       <c r="H31" s="35">
-        <v>30000</v>
+        <v>13100</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>50</v>
@@ -1881,7 +1885,7 @@
       </c>
       <c r="H32" s="41">
         <f>H30+H31</f>
-        <v>267390</v>
+        <v>250490</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>14</v>
@@ -1906,7 +1910,7 @@
       </c>
       <c r="H33" s="45">
         <f>H29-H32</f>
-        <v>-112436.56400000001</v>
+        <v>-95536.564000000013</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>15</v>
@@ -1955,7 +1959,7 @@
       </c>
       <c r="H35" s="42">
         <f>H33+H34</f>
-        <v>-55436.564000000013</v>
+        <v>-38536.564000000013</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>31</v>
@@ -2009,7 +2013,7 @@
       </c>
       <c r="H38" s="32">
         <f>H37-H32</f>
-        <v>108160.80599999998</v>
+        <v>125060.80599999998</v>
       </c>
       <c r="I38" s="91" t="s">
         <v>65</v>
